--- a/tame_output/ON/bt/strategyON_20230822.xlsx
+++ b/tame_output/ON/bt/strategyON_20230822.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,17 +623,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -748,26 +748,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1696"/>
+  <dimension ref="A1:G1697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40518,7 +40518,7 @@
         <v>45158</v>
       </c>
       <c r="B1696" t="n">
-        <v>2.770362411625738</v>
+        <v>2.769733035826329</v>
       </c>
       <c r="C1696" t="n">
         <v>2.890170122691142</v>
@@ -40534,6 +40534,29 @@
       </c>
       <c r="G1696" t="n">
         <v>4.196996947650614</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="2" t="n">
+        <v>45159</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>2.767457125596384</v>
+      </c>
+      <c r="C1697" t="n">
+        <v>2.896213149298758</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>1.559957365371448</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>3.51983967113359</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>2.180334500356101</v>
+      </c>
+      <c r="G1697" t="n">
+        <v>4.20441384951242</v>
       </c>
     </row>
   </sheetData>
